--- a/data.mn/public/datasets/mongolbank-external-debt.xlsx
+++ b/data.mn/public/datasets/mongolbank-external-debt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,8 +414,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1436,7 +1440,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>38042.62</v>
+        <v>37885.31</v>
       </c>
     </row>
     <row r="103">
@@ -1446,7 +1450,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>39612.48</v>
+        <v>38986.17</v>
       </c>
     </row>
     <row r="104">
@@ -1456,7 +1460,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>40439.32</v>
+        <v>40280.4</v>
       </c>
     </row>
     <row r="105">
@@ -1466,7 +1470,17 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>40460.18</v>
+        <v>40277.42</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>40217.55</v>
       </c>
     </row>
   </sheetData>
@@ -1480,8 +1494,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2502,7 +2520,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>38042.62</v>
+        <v>37885.31</v>
       </c>
     </row>
     <row r="103">
@@ -2512,7 +2530,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>39612.48</v>
+        <v>38986.17</v>
       </c>
     </row>
     <row r="104">
@@ -2522,7 +2540,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>40439.32</v>
+        <v>40280.4</v>
       </c>
     </row>
     <row r="105">
@@ -2532,7 +2550,17 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>40460.18</v>
+        <v>40277.42</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>40217.55</v>
       </c>
     </row>
   </sheetData>
